--- a/data/trans_dic/IP31KM06_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM06_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,2; 32,07</t>
+          <t>25,26; 48,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,92; 50,18</t>
+          <t>19,35; 33,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,06; 40,41</t>
+          <t>24,9; 37,97</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,53; 32,75</t>
+          <t>30,39; 42,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,11; 41,28</t>
+          <t>23,32; 35,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,68; 35,99</t>
+          <t>28,51; 37,15</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,31; 66,15</t>
+          <t>34,58; 50,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,66; 50,31</t>
+          <t>30,02; 43,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,96; 58,28</t>
+          <t>34,98; 44,66</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,56; 47,73</t>
+          <t>35,77; 48,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,32; 49,48</t>
+          <t>37,03; 50,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,38; 46,92</t>
+          <t>38,26; 47,62</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,93; 44,02</t>
+          <t>35,12; 42,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,22; 42,3</t>
+          <t>30,99; 37,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,28; 41,2</t>
+          <t>34,02; 39,28</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28808</t>
+          <t>42125</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45062</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73869</t>
+          <t>73023</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21932; 36635</t>
+          <t>31047; 60061</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31363; 68651</t>
+          <t>22946; 39839</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60403; 101461</t>
+          <t>60138; 91688</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>74</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>50421</t>
+          <t>82517</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>85917</t>
+          <t>52241</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>136338</t>
+          <t>134757</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40064; 60954</t>
+          <t>70263; 97857</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72044; 102185</t>
+          <t>42106; 63274</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>120011; 156069</t>
+          <t>117407; 152977</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82520</t>
+          <t>70960</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78435</t>
+          <t>56810</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160955</t>
+          <t>127770</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>60832; 124533</t>
+          <t>57584; 84716</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65296; 92107</t>
+          <t>46536; 66710</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137263; 216408</t>
+          <t>112495; 143614</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>68381</t>
+          <t>69581</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>74920</t>
+          <t>71253</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143302</t>
+          <t>140834</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58511; 78519</t>
+          <t>59431; 80622</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64398; 87727</t>
+          <t>60723; 82038</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>127780; 160379</t>
+          <t>126315; 157215</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>290</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>230130</t>
+          <t>265182</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>284334</t>
+          <t>211202</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>514464</t>
+          <t>476384</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>202004; 287541</t>
+          <t>241225; 291196</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>254866; 315021</t>
+          <t>191598; 234513</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>479166; 575961</t>
+          <t>444019; 512656</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM06_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM06_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que acuden una vez o más a la semana a un centro de comida rápida (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>34,28%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>26,05%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>25,26; 48,87</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>19,35; 33,59</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24,9; 37,97</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>35,68%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>28,93%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>32,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>30,39; 42,32</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>23,32; 35,04</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>28,51; 37,15</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>42,61%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>36,64%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39,73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>34,58; 50,87</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30,02; 43,03</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>34,98; 44,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>41,87%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>43,45%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>42,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>35,77; 48,52</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>37,03; 50,03</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>38,26; 47,62</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>38,61%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>34,16%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>36,5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>35,12; 42,4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>30,99; 37,93</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34,02; 39,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.3427661146553234</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2605318686706573</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.3023808886549341</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>42125</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>30899</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>73023</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.2526256886746043</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1934737105771295</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.2490261535479249</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>31047; 60061</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>22946; 39839</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>60138; 91688</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.4887133008841426</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.3359124915590757</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.3796688490449155</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.3568432304314708</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.2892721951248373</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.3272126932423573</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>82517</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>52241</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>134757</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.303850680674817</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.2331552789276336</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.285083160420212</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>70263; 97857</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>42106; 63274</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>117407; 152977</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.4231815617424411</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.3503692251157904</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.371454906593764</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4261269552776707</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3664272539880387</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.3973431093856579</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>70960</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>56810</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>127770</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.3458063382261923</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.300159562125944</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.3498408844768468</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>57584; 84716</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>46536; 66710</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>112495; 143614</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5087388886179387</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4302821047266653</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.4466165323340058</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4187479747685084</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4345256647883163</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4265845855431837</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>69581</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>71253</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>140834</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.3576648684816237</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.3703120908813924</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.3826051685371212</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>59431; 80622</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>60723; 82038</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>126315; 157215</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.4851914670249682</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5002973975751257</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.476200700242964</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.3860990997494866</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.3416364053299036</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.3650366333780123</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>265182</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>211202</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>476384</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.3512185179999625</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.3099249400451485</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.3402364075073516</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>241225; 291196</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>191598; 234513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>444019; 512656</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.4239741178621034</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.3793427307052015</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.392830887834407</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que acuden una vez o más a la semana a un centro de comida rápida (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>42125</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>30899</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>73023</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>31047</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>22946</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>60138</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>60061</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>39839</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>91688</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>82517</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>52241</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>134757</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>70263</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>42106</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>117407</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>97857</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>63274</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>152977</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>70960</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>56810</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>127770</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>57584</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>46536</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>112495</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>84716</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>66710</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>143614</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>69581</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>71253</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>140834</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>59431</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>60723</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>126315</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>80622</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>82038</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>157215</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>332</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>290</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>265182</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>211202</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>476384</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>241225</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>191598</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>444019</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>291196</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>234513</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>512656</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>